--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.9</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,37 +533,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.3</t>
+          <t>00:019.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>111.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.31</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40477</t>
+          <t>122238</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.8</t>
+          <t>00:030.4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>118.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>255810</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>89003</t>
+          <t>284130</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.1</t>
+          <t>00:049.4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>124326</t>
+          <t>359977</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.1</t>
+          <t>01:000.4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>110.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>172256</t>
+          <t>476351</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.6</t>
+          <t>01:009.5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>107.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>192000</t>
+          <t>578000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:020.2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>195577</t>
+          <t>676764</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -937,22 +937,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>193923</t>
+          <t>791642</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:040.3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>196969</t>
+          <t>926218</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1039,34 +1039,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.0</t>
+          <t>01:050.3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>127.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>218884</t>
+          <t>1036970</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:060.0</t>
+          <t>01:059.7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>233721</t>
+          <t>1102331</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.8</t>
+          <t>02:009.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>119.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>231964</t>
+          <t>1188060</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,34 +1210,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:021.6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>111.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14.18</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>256395</t>
+          <t>1273773</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.2</t>
+          <t>02:030.8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>276967</t>
+          <t>1335758</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1324,34 +1324,34 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.0</t>
+          <t>02:039.6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>284431</t>
+          <t>1361213</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.2</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>286455</t>
+          <t>1342556</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.3</t>
+          <t>02:055.6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>278675</t>
+          <t>1330943</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,6 +1494,63 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>44.1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1330362</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>

--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.1</t>
+          <t>00:010.4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,32 +538,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>111.3</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>50.19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>122238</t>
+          <t>177933</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.4</t>
+          <t>00:029.7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.6</t>
+          <t>134.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>255810</t>
+          <t>407909</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.0</t>
+          <t>00:039.3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>284130</t>
+          <t>478565</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.4</t>
+          <t>00:050.0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>110.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>359977</t>
+          <t>553760</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.4</t>
+          <t>00:059.7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>110.9</t>
+          <t>134.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>476351</t>
+          <t>671809</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,22 +818,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.5</t>
+          <t>01:009.9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>107.3</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>578000</t>
+          <t>785773</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,22 +875,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.2</t>
+          <t>01:020.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>114.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>676764</t>
+          <t>879356</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,22 +932,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.9</t>
+          <t>01:029.7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>791642</t>
+          <t>949004</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,22 +989,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.3</t>
+          <t>01:039.7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>926218</t>
+          <t>1003676</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.3</t>
+          <t>01:049.7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1036970</t>
+          <t>1049604</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.7</t>
+          <t>02:000.4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1102331</t>
+          <t>1104580</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.0</t>
+          <t>02:010.3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>119.7</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1188060</t>
+          <t>1173803</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:021.6</t>
+          <t>02:020.2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1273773</t>
+          <t>1249160</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.8</t>
+          <t>02:029.9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>110.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1335758</t>
+          <t>1337464</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1324,34 +1324,34 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.6</t>
+          <t>02:040.1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1361213</t>
+          <t>1381975</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.0</t>
+          <t>02:048.7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1342556</t>
+          <t>1372683</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.6</t>
+          <t>02:055.0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1330943</t>
+          <t>1365947</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1507,22 +1507,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1330362</t>
+          <t>1365962</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
